--- a/椙山改修/参考/261031_施工計画書_雛形（修正版）.xlsx
+++ b/椙山改修/参考/261031_施工計画書_雛形（修正版）.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="dddd&quot;, &quot;mmmm&quot; &quot;dd&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="31">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <color indexed="8"/>
@@ -155,19 +155,9 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
-      <color rgb="00FF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="ＭＳ 明朝"/>
       <color rgb="00FF0000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="00FF0000"/>
-      <sz val="14"/>
     </font>
     <font>
       <name val="HG丸ｺﾞｼｯｸM-PRO"/>
@@ -517,7 +507,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -768,9 +758,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -781,40 +768,31 @@
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="25" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="26" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="27" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2022,82 +2000,82 @@
       <c r="AI4" s="2" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="83">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事</t>
         </is>
       </c>
-      <c r="B5" s="85" t="n"/>
-      <c r="C5" s="85" t="n"/>
-      <c r="D5" s="85" t="n"/>
-      <c r="E5" s="85" t="n"/>
-      <c r="F5" s="85" t="n"/>
-      <c r="G5" s="85" t="n"/>
-      <c r="H5" s="85" t="n"/>
-      <c r="I5" s="85" t="n"/>
-      <c r="J5" s="85" t="n"/>
-      <c r="K5" s="85" t="n"/>
-      <c r="L5" s="85" t="n"/>
-      <c r="M5" s="85" t="n"/>
-      <c r="N5" s="85" t="n"/>
-      <c r="O5" s="85" t="n"/>
-      <c r="P5" s="85" t="n"/>
-      <c r="Q5" s="85" t="n"/>
-      <c r="R5" s="85" t="n"/>
-      <c r="S5" s="85" t="n"/>
-      <c r="T5" s="85" t="n"/>
-      <c r="U5" s="85" t="n"/>
-      <c r="V5" s="85" t="n"/>
-      <c r="W5" s="85" t="n"/>
-      <c r="X5" s="85" t="n"/>
-      <c r="Y5" s="85" t="n"/>
-      <c r="Z5" s="85" t="n"/>
-      <c r="AA5" s="85" t="n"/>
-      <c r="AB5" s="85" t="n"/>
-      <c r="AC5" s="85" t="n"/>
-      <c r="AD5" s="85" t="n"/>
-      <c r="AE5" s="85" t="n"/>
-      <c r="AF5" s="85" t="n"/>
-      <c r="AG5" s="85" t="n"/>
-      <c r="AH5" s="85" t="n"/>
-      <c r="AI5" s="86" t="n"/>
+      <c r="B5" s="84" t="n"/>
+      <c r="C5" s="84" t="n"/>
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="n"/>
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="n"/>
+      <c r="L5" s="84" t="n"/>
+      <c r="M5" s="84" t="n"/>
+      <c r="N5" s="84" t="n"/>
+      <c r="O5" s="84" t="n"/>
+      <c r="P5" s="84" t="n"/>
+      <c r="Q5" s="84" t="n"/>
+      <c r="R5" s="84" t="n"/>
+      <c r="S5" s="84" t="n"/>
+      <c r="T5" s="84" t="n"/>
+      <c r="U5" s="84" t="n"/>
+      <c r="V5" s="84" t="n"/>
+      <c r="W5" s="84" t="n"/>
+      <c r="X5" s="84" t="n"/>
+      <c r="Y5" s="84" t="n"/>
+      <c r="Z5" s="84" t="n"/>
+      <c r="AA5" s="84" t="n"/>
+      <c r="AB5" s="84" t="n"/>
+      <c r="AC5" s="84" t="n"/>
+      <c r="AD5" s="84" t="n"/>
+      <c r="AE5" s="84" t="n"/>
+      <c r="AF5" s="84" t="n"/>
+      <c r="AG5" s="84" t="n"/>
+      <c r="AH5" s="84" t="n"/>
+      <c r="AI5" s="85" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="83">
-      <c r="A6" s="87" t="n"/>
-      <c r="B6" s="88" t="n"/>
-      <c r="C6" s="88" t="n"/>
-      <c r="D6" s="88" t="n"/>
-      <c r="E6" s="88" t="n"/>
-      <c r="F6" s="88" t="n"/>
-      <c r="G6" s="88" t="n"/>
-      <c r="H6" s="88" t="n"/>
-      <c r="I6" s="88" t="n"/>
-      <c r="J6" s="88" t="n"/>
-      <c r="K6" s="88" t="n"/>
-      <c r="L6" s="88" t="n"/>
-      <c r="M6" s="88" t="n"/>
-      <c r="N6" s="88" t="n"/>
-      <c r="O6" s="88" t="n"/>
-      <c r="P6" s="88" t="n"/>
-      <c r="Q6" s="88" t="n"/>
-      <c r="R6" s="88" t="n"/>
-      <c r="S6" s="88" t="n"/>
-      <c r="T6" s="88" t="n"/>
-      <c r="U6" s="88" t="n"/>
-      <c r="V6" s="88" t="n"/>
-      <c r="W6" s="88" t="n"/>
-      <c r="X6" s="88" t="n"/>
-      <c r="Y6" s="88" t="n"/>
-      <c r="Z6" s="88" t="n"/>
-      <c r="AA6" s="88" t="n"/>
-      <c r="AB6" s="88" t="n"/>
-      <c r="AC6" s="88" t="n"/>
-      <c r="AD6" s="88" t="n"/>
-      <c r="AE6" s="88" t="n"/>
-      <c r="AF6" s="88" t="n"/>
-      <c r="AG6" s="88" t="n"/>
-      <c r="AH6" s="88" t="n"/>
-      <c r="AI6" s="89" t="n"/>
+      <c r="A6" s="86" t="n"/>
+      <c r="B6" s="87" t="n"/>
+      <c r="C6" s="87" t="n"/>
+      <c r="D6" s="87" t="n"/>
+      <c r="E6" s="87" t="n"/>
+      <c r="F6" s="87" t="n"/>
+      <c r="G6" s="87" t="n"/>
+      <c r="H6" s="87" t="n"/>
+      <c r="I6" s="87" t="n"/>
+      <c r="J6" s="87" t="n"/>
+      <c r="K6" s="87" t="n"/>
+      <c r="L6" s="87" t="n"/>
+      <c r="M6" s="87" t="n"/>
+      <c r="N6" s="87" t="n"/>
+      <c r="O6" s="87" t="n"/>
+      <c r="P6" s="87" t="n"/>
+      <c r="Q6" s="87" t="n"/>
+      <c r="R6" s="87" t="n"/>
+      <c r="S6" s="87" t="n"/>
+      <c r="T6" s="87" t="n"/>
+      <c r="U6" s="87" t="n"/>
+      <c r="V6" s="87" t="n"/>
+      <c r="W6" s="87" t="n"/>
+      <c r="X6" s="87" t="n"/>
+      <c r="Y6" s="87" t="n"/>
+      <c r="Z6" s="87" t="n"/>
+      <c r="AA6" s="87" t="n"/>
+      <c r="AB6" s="87" t="n"/>
+      <c r="AC6" s="87" t="n"/>
+      <c r="AD6" s="87" t="n"/>
+      <c r="AE6" s="87" t="n"/>
+      <c r="AF6" s="87" t="n"/>
+      <c r="AG6" s="87" t="n"/>
+      <c r="AH6" s="87" t="n"/>
+      <c r="AI6" s="88" t="n"/>
     </row>
     <row r="7" ht="13.5" customHeight="1" s="83">
       <c r="A7" s="2" t="n"/>
@@ -2364,77 +2342,77 @@
           <t>（■■工事名）工事施工計画書</t>
         </is>
       </c>
-      <c r="B14" s="85" t="n"/>
-      <c r="C14" s="85" t="n"/>
-      <c r="D14" s="85" t="n"/>
-      <c r="E14" s="85" t="n"/>
-      <c r="F14" s="85" t="n"/>
-      <c r="G14" s="85" t="n"/>
-      <c r="H14" s="85" t="n"/>
-      <c r="I14" s="85" t="n"/>
-      <c r="J14" s="85" t="n"/>
-      <c r="K14" s="85" t="n"/>
-      <c r="L14" s="85" t="n"/>
-      <c r="M14" s="85" t="n"/>
-      <c r="N14" s="85" t="n"/>
-      <c r="O14" s="85" t="n"/>
-      <c r="P14" s="85" t="n"/>
-      <c r="Q14" s="85" t="n"/>
-      <c r="R14" s="85" t="n"/>
-      <c r="S14" s="85" t="n"/>
-      <c r="T14" s="85" t="n"/>
-      <c r="U14" s="85" t="n"/>
-      <c r="V14" s="85" t="n"/>
-      <c r="W14" s="85" t="n"/>
-      <c r="X14" s="85" t="n"/>
-      <c r="Y14" s="85" t="n"/>
-      <c r="Z14" s="85" t="n"/>
-      <c r="AA14" s="85" t="n"/>
-      <c r="AB14" s="85" t="n"/>
-      <c r="AC14" s="85" t="n"/>
-      <c r="AD14" s="85" t="n"/>
-      <c r="AE14" s="85" t="n"/>
-      <c r="AF14" s="85" t="n"/>
-      <c r="AG14" s="85" t="n"/>
-      <c r="AH14" s="85" t="n"/>
-      <c r="AI14" s="86" t="n"/>
+      <c r="B14" s="84" t="n"/>
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="84" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="84" t="n"/>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="84" t="n"/>
+      <c r="I14" s="84" t="n"/>
+      <c r="J14" s="84" t="n"/>
+      <c r="K14" s="84" t="n"/>
+      <c r="L14" s="84" t="n"/>
+      <c r="M14" s="84" t="n"/>
+      <c r="N14" s="84" t="n"/>
+      <c r="O14" s="84" t="n"/>
+      <c r="P14" s="84" t="n"/>
+      <c r="Q14" s="84" t="n"/>
+      <c r="R14" s="84" t="n"/>
+      <c r="S14" s="84" t="n"/>
+      <c r="T14" s="84" t="n"/>
+      <c r="U14" s="84" t="n"/>
+      <c r="V14" s="84" t="n"/>
+      <c r="W14" s="84" t="n"/>
+      <c r="X14" s="84" t="n"/>
+      <c r="Y14" s="84" t="n"/>
+      <c r="Z14" s="84" t="n"/>
+      <c r="AA14" s="84" t="n"/>
+      <c r="AB14" s="84" t="n"/>
+      <c r="AC14" s="84" t="n"/>
+      <c r="AD14" s="84" t="n"/>
+      <c r="AE14" s="84" t="n"/>
+      <c r="AF14" s="84" t="n"/>
+      <c r="AG14" s="84" t="n"/>
+      <c r="AH14" s="84" t="n"/>
+      <c r="AI14" s="85" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="83">
-      <c r="A15" s="87" t="n"/>
-      <c r="B15" s="88" t="n"/>
-      <c r="C15" s="88" t="n"/>
-      <c r="D15" s="88" t="n"/>
-      <c r="E15" s="88" t="n"/>
-      <c r="F15" s="88" t="n"/>
-      <c r="G15" s="88" t="n"/>
-      <c r="H15" s="88" t="n"/>
-      <c r="I15" s="88" t="n"/>
-      <c r="J15" s="88" t="n"/>
-      <c r="K15" s="88" t="n"/>
-      <c r="L15" s="88" t="n"/>
-      <c r="M15" s="88" t="n"/>
-      <c r="N15" s="88" t="n"/>
-      <c r="O15" s="88" t="n"/>
-      <c r="P15" s="88" t="n"/>
-      <c r="Q15" s="88" t="n"/>
-      <c r="R15" s="88" t="n"/>
-      <c r="S15" s="88" t="n"/>
-      <c r="T15" s="88" t="n"/>
-      <c r="U15" s="88" t="n"/>
-      <c r="V15" s="88" t="n"/>
-      <c r="W15" s="88" t="n"/>
-      <c r="X15" s="88" t="n"/>
-      <c r="Y15" s="88" t="n"/>
-      <c r="Z15" s="88" t="n"/>
-      <c r="AA15" s="88" t="n"/>
-      <c r="AB15" s="88" t="n"/>
-      <c r="AC15" s="88" t="n"/>
-      <c r="AD15" s="88" t="n"/>
-      <c r="AE15" s="88" t="n"/>
-      <c r="AF15" s="88" t="n"/>
-      <c r="AG15" s="88" t="n"/>
-      <c r="AH15" s="88" t="n"/>
-      <c r="AI15" s="89" t="n"/>
+      <c r="A15" s="86" t="n"/>
+      <c r="B15" s="87" t="n"/>
+      <c r="C15" s="87" t="n"/>
+      <c r="D15" s="87" t="n"/>
+      <c r="E15" s="87" t="n"/>
+      <c r="F15" s="87" t="n"/>
+      <c r="G15" s="87" t="n"/>
+      <c r="H15" s="87" t="n"/>
+      <c r="I15" s="87" t="n"/>
+      <c r="J15" s="87" t="n"/>
+      <c r="K15" s="87" t="n"/>
+      <c r="L15" s="87" t="n"/>
+      <c r="M15" s="87" t="n"/>
+      <c r="N15" s="87" t="n"/>
+      <c r="O15" s="87" t="n"/>
+      <c r="P15" s="87" t="n"/>
+      <c r="Q15" s="87" t="n"/>
+      <c r="R15" s="87" t="n"/>
+      <c r="S15" s="87" t="n"/>
+      <c r="T15" s="87" t="n"/>
+      <c r="U15" s="87" t="n"/>
+      <c r="V15" s="87" t="n"/>
+      <c r="W15" s="87" t="n"/>
+      <c r="X15" s="87" t="n"/>
+      <c r="Y15" s="87" t="n"/>
+      <c r="Z15" s="87" t="n"/>
+      <c r="AA15" s="87" t="n"/>
+      <c r="AB15" s="87" t="n"/>
+      <c r="AC15" s="87" t="n"/>
+      <c r="AD15" s="87" t="n"/>
+      <c r="AE15" s="87" t="n"/>
+      <c r="AF15" s="87" t="n"/>
+      <c r="AG15" s="87" t="n"/>
+      <c r="AH15" s="87" t="n"/>
+      <c r="AI15" s="88" t="n"/>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="83">
       <c r="A16" s="2" t="n"/>
@@ -2886,77 +2864,77 @@
           <t>令和8年　■月</t>
         </is>
       </c>
-      <c r="B28" s="85" t="n"/>
-      <c r="C28" s="85" t="n"/>
-      <c r="D28" s="85" t="n"/>
-      <c r="E28" s="85" t="n"/>
-      <c r="F28" s="85" t="n"/>
-      <c r="G28" s="85" t="n"/>
-      <c r="H28" s="85" t="n"/>
-      <c r="I28" s="85" t="n"/>
-      <c r="J28" s="85" t="n"/>
-      <c r="K28" s="85" t="n"/>
-      <c r="L28" s="85" t="n"/>
-      <c r="M28" s="85" t="n"/>
-      <c r="N28" s="85" t="n"/>
-      <c r="O28" s="85" t="n"/>
-      <c r="P28" s="85" t="n"/>
-      <c r="Q28" s="85" t="n"/>
-      <c r="R28" s="85" t="n"/>
-      <c r="S28" s="85" t="n"/>
-      <c r="T28" s="85" t="n"/>
-      <c r="U28" s="85" t="n"/>
-      <c r="V28" s="85" t="n"/>
-      <c r="W28" s="85" t="n"/>
-      <c r="X28" s="85" t="n"/>
-      <c r="Y28" s="85" t="n"/>
-      <c r="Z28" s="85" t="n"/>
-      <c r="AA28" s="85" t="n"/>
-      <c r="AB28" s="85" t="n"/>
-      <c r="AC28" s="85" t="n"/>
-      <c r="AD28" s="85" t="n"/>
-      <c r="AE28" s="85" t="n"/>
-      <c r="AF28" s="85" t="n"/>
-      <c r="AG28" s="85" t="n"/>
-      <c r="AH28" s="85" t="n"/>
-      <c r="AI28" s="86" t="n"/>
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="84" t="n"/>
+      <c r="I28" s="84" t="n"/>
+      <c r="J28" s="84" t="n"/>
+      <c r="K28" s="84" t="n"/>
+      <c r="L28" s="84" t="n"/>
+      <c r="M28" s="84" t="n"/>
+      <c r="N28" s="84" t="n"/>
+      <c r="O28" s="84" t="n"/>
+      <c r="P28" s="84" t="n"/>
+      <c r="Q28" s="84" t="n"/>
+      <c r="R28" s="84" t="n"/>
+      <c r="S28" s="84" t="n"/>
+      <c r="T28" s="84" t="n"/>
+      <c r="U28" s="84" t="n"/>
+      <c r="V28" s="84" t="n"/>
+      <c r="W28" s="84" t="n"/>
+      <c r="X28" s="84" t="n"/>
+      <c r="Y28" s="84" t="n"/>
+      <c r="Z28" s="84" t="n"/>
+      <c r="AA28" s="84" t="n"/>
+      <c r="AB28" s="84" t="n"/>
+      <c r="AC28" s="84" t="n"/>
+      <c r="AD28" s="84" t="n"/>
+      <c r="AE28" s="84" t="n"/>
+      <c r="AF28" s="84" t="n"/>
+      <c r="AG28" s="84" t="n"/>
+      <c r="AH28" s="84" t="n"/>
+      <c r="AI28" s="85" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="83">
-      <c r="A29" s="87" t="n"/>
-      <c r="B29" s="88" t="n"/>
-      <c r="C29" s="88" t="n"/>
-      <c r="D29" s="88" t="n"/>
-      <c r="E29" s="88" t="n"/>
-      <c r="F29" s="88" t="n"/>
-      <c r="G29" s="88" t="n"/>
-      <c r="H29" s="88" t="n"/>
-      <c r="I29" s="88" t="n"/>
-      <c r="J29" s="88" t="n"/>
-      <c r="K29" s="88" t="n"/>
-      <c r="L29" s="88" t="n"/>
-      <c r="M29" s="88" t="n"/>
-      <c r="N29" s="88" t="n"/>
-      <c r="O29" s="88" t="n"/>
-      <c r="P29" s="88" t="n"/>
-      <c r="Q29" s="88" t="n"/>
-      <c r="R29" s="88" t="n"/>
-      <c r="S29" s="88" t="n"/>
-      <c r="T29" s="88" t="n"/>
-      <c r="U29" s="88" t="n"/>
-      <c r="V29" s="88" t="n"/>
-      <c r="W29" s="88" t="n"/>
-      <c r="X29" s="88" t="n"/>
-      <c r="Y29" s="88" t="n"/>
-      <c r="Z29" s="88" t="n"/>
-      <c r="AA29" s="88" t="n"/>
-      <c r="AB29" s="88" t="n"/>
-      <c r="AC29" s="88" t="n"/>
-      <c r="AD29" s="88" t="n"/>
-      <c r="AE29" s="88" t="n"/>
-      <c r="AF29" s="88" t="n"/>
-      <c r="AG29" s="88" t="n"/>
-      <c r="AH29" s="88" t="n"/>
-      <c r="AI29" s="89" t="n"/>
+      <c r="A29" s="86" t="n"/>
+      <c r="B29" s="87" t="n"/>
+      <c r="C29" s="87" t="n"/>
+      <c r="D29" s="87" t="n"/>
+      <c r="E29" s="87" t="n"/>
+      <c r="F29" s="87" t="n"/>
+      <c r="G29" s="87" t="n"/>
+      <c r="H29" s="87" t="n"/>
+      <c r="I29" s="87" t="n"/>
+      <c r="J29" s="87" t="n"/>
+      <c r="K29" s="87" t="n"/>
+      <c r="L29" s="87" t="n"/>
+      <c r="M29" s="87" t="n"/>
+      <c r="N29" s="87" t="n"/>
+      <c r="O29" s="87" t="n"/>
+      <c r="P29" s="87" t="n"/>
+      <c r="Q29" s="87" t="n"/>
+      <c r="R29" s="87" t="n"/>
+      <c r="S29" s="87" t="n"/>
+      <c r="T29" s="87" t="n"/>
+      <c r="U29" s="87" t="n"/>
+      <c r="V29" s="87" t="n"/>
+      <c r="W29" s="87" t="n"/>
+      <c r="X29" s="87" t="n"/>
+      <c r="Y29" s="87" t="n"/>
+      <c r="Z29" s="87" t="n"/>
+      <c r="AA29" s="87" t="n"/>
+      <c r="AB29" s="87" t="n"/>
+      <c r="AC29" s="87" t="n"/>
+      <c r="AD29" s="87" t="n"/>
+      <c r="AE29" s="87" t="n"/>
+      <c r="AF29" s="87" t="n"/>
+      <c r="AG29" s="87" t="n"/>
+      <c r="AH29" s="87" t="n"/>
+      <c r="AI29" s="88" t="n"/>
     </row>
     <row r="30" ht="13.2" customHeight="1" s="83">
       <c r="A30" s="2" t="n"/>
@@ -3081,20 +3059,20 @@
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="7" t="n"/>
-      <c r="L33" s="90" t="n"/>
-      <c r="M33" s="90" t="n"/>
-      <c r="N33" s="90" t="n"/>
-      <c r="O33" s="90" t="n"/>
-      <c r="P33" s="90" t="n"/>
-      <c r="Q33" s="90" t="n"/>
-      <c r="R33" s="90" t="n"/>
-      <c r="S33" s="90" t="n"/>
-      <c r="T33" s="90" t="n"/>
-      <c r="U33" s="90" t="n"/>
-      <c r="V33" s="90" t="n"/>
-      <c r="W33" s="90" t="n"/>
-      <c r="X33" s="90" t="n"/>
-      <c r="Y33" s="91" t="n"/>
+      <c r="L33" s="89" t="n"/>
+      <c r="M33" s="89" t="n"/>
+      <c r="N33" s="89" t="n"/>
+      <c r="O33" s="89" t="n"/>
+      <c r="P33" s="89" t="n"/>
+      <c r="Q33" s="89" t="n"/>
+      <c r="R33" s="89" t="n"/>
+      <c r="S33" s="89" t="n"/>
+      <c r="T33" s="89" t="n"/>
+      <c r="U33" s="89" t="n"/>
+      <c r="V33" s="89" t="n"/>
+      <c r="W33" s="89" t="n"/>
+      <c r="X33" s="89" t="n"/>
+      <c r="Y33" s="90" t="n"/>
       <c r="Z33" s="2" t="n"/>
       <c r="AA33" s="2" t="n"/>
       <c r="AB33" s="2" t="n"/>
@@ -3118,20 +3096,20 @@
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="8" t="n"/>
-      <c r="L34" s="90" t="n"/>
-      <c r="M34" s="90" t="n"/>
-      <c r="N34" s="90" t="n"/>
-      <c r="O34" s="91" t="n"/>
+      <c r="L34" s="89" t="n"/>
+      <c r="M34" s="89" t="n"/>
+      <c r="N34" s="89" t="n"/>
+      <c r="O34" s="90" t="n"/>
       <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="90" t="n"/>
-      <c r="R34" s="90" t="n"/>
-      <c r="S34" s="90" t="n"/>
-      <c r="T34" s="91" t="n"/>
+      <c r="Q34" s="89" t="n"/>
+      <c r="R34" s="89" t="n"/>
+      <c r="S34" s="89" t="n"/>
+      <c r="T34" s="90" t="n"/>
       <c r="U34" s="8" t="n"/>
-      <c r="V34" s="90" t="n"/>
-      <c r="W34" s="90" t="n"/>
-      <c r="X34" s="90" t="n"/>
-      <c r="Y34" s="91" t="n"/>
+      <c r="V34" s="89" t="n"/>
+      <c r="W34" s="89" t="n"/>
+      <c r="X34" s="89" t="n"/>
+      <c r="Y34" s="90" t="n"/>
       <c r="Z34" s="2" t="n"/>
       <c r="AA34" s="2" t="n"/>
       <c r="AB34" s="2" t="n"/>
@@ -3340,20 +3318,20 @@
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="8" t="n"/>
-      <c r="L40" s="90" t="n"/>
-      <c r="M40" s="90" t="n"/>
-      <c r="N40" s="90" t="n"/>
-      <c r="O40" s="90" t="n"/>
-      <c r="P40" s="90" t="n"/>
-      <c r="Q40" s="90" t="n"/>
-      <c r="R40" s="90" t="n"/>
-      <c r="S40" s="90" t="n"/>
-      <c r="T40" s="90" t="n"/>
-      <c r="U40" s="90" t="n"/>
-      <c r="V40" s="90" t="n"/>
-      <c r="W40" s="90" t="n"/>
-      <c r="X40" s="90" t="n"/>
-      <c r="Y40" s="91" t="n"/>
+      <c r="L40" s="89" t="n"/>
+      <c r="M40" s="89" t="n"/>
+      <c r="N40" s="89" t="n"/>
+      <c r="O40" s="89" t="n"/>
+      <c r="P40" s="89" t="n"/>
+      <c r="Q40" s="89" t="n"/>
+      <c r="R40" s="89" t="n"/>
+      <c r="S40" s="89" t="n"/>
+      <c r="T40" s="89" t="n"/>
+      <c r="U40" s="89" t="n"/>
+      <c r="V40" s="89" t="n"/>
+      <c r="W40" s="89" t="n"/>
+      <c r="X40" s="89" t="n"/>
+      <c r="Y40" s="90" t="n"/>
       <c r="Z40" s="2" t="n"/>
       <c r="AA40" s="2" t="n"/>
       <c r="AB40" s="2" t="n"/>
@@ -3377,20 +3355,20 @@
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="8" t="n"/>
-      <c r="L41" s="90" t="n"/>
-      <c r="M41" s="90" t="n"/>
-      <c r="N41" s="90" t="n"/>
-      <c r="O41" s="91" t="n"/>
+      <c r="L41" s="89" t="n"/>
+      <c r="M41" s="89" t="n"/>
+      <c r="N41" s="89" t="n"/>
+      <c r="O41" s="90" t="n"/>
       <c r="P41" s="8" t="n"/>
-      <c r="Q41" s="90" t="n"/>
-      <c r="R41" s="90" t="n"/>
-      <c r="S41" s="90" t="n"/>
-      <c r="T41" s="91" t="n"/>
+      <c r="Q41" s="89" t="n"/>
+      <c r="R41" s="89" t="n"/>
+      <c r="S41" s="89" t="n"/>
+      <c r="T41" s="90" t="n"/>
       <c r="U41" s="8" t="n"/>
-      <c r="V41" s="90" t="n"/>
-      <c r="W41" s="90" t="n"/>
-      <c r="X41" s="90" t="n"/>
-      <c r="Y41" s="91" t="n"/>
+      <c r="V41" s="89" t="n"/>
+      <c r="W41" s="89" t="n"/>
+      <c r="X41" s="89" t="n"/>
+      <c r="Y41" s="90" t="n"/>
       <c r="Z41" s="2" t="n"/>
       <c r="AA41" s="2" t="n"/>
       <c r="AB41" s="2" t="n"/>
@@ -3657,8 +3635,8 @@
       <c r="Z2" s="13" t="n"/>
       <c r="AA2" s="13" t="n"/>
       <c r="AB2" s="14" t="n"/>
-      <c r="AC2" s="90" t="n"/>
-      <c r="AD2" s="91" t="n"/>
+      <c r="AC2" s="89" t="n"/>
+      <c r="AD2" s="90" t="n"/>
     </row>
     <row r="3" ht="16.5" customHeight="1" s="83">
       <c r="A3" s="2" t="n"/>
@@ -3693,8 +3671,8 @@
       <c r="Z3" s="13" t="n"/>
       <c r="AA3" s="13" t="n"/>
       <c r="AB3" s="14" t="n"/>
-      <c r="AC3" s="90" t="n"/>
-      <c r="AD3" s="91" t="n"/>
+      <c r="AC3" s="89" t="n"/>
+      <c r="AD3" s="90" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="83">
       <c r="A4" s="2" t="n"/>
@@ -3733,8 +3711,8 @@
       <c r="Z4" s="13" t="n"/>
       <c r="AA4" s="13" t="n"/>
       <c r="AB4" s="14" t="n"/>
-      <c r="AC4" s="90" t="n"/>
-      <c r="AD4" s="91" t="n"/>
+      <c r="AC4" s="89" t="n"/>
+      <c r="AD4" s="90" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="83">
       <c r="A5" s="2" t="n"/>
@@ -3773,8 +3751,8 @@
       <c r="Z5" s="13" t="n"/>
       <c r="AA5" s="13" t="n"/>
       <c r="AB5" s="14" t="n"/>
-      <c r="AC5" s="90" t="n"/>
-      <c r="AD5" s="91" t="n"/>
+      <c r="AC5" s="89" t="n"/>
+      <c r="AD5" s="90" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="83">
       <c r="A6" s="2" t="n"/>
@@ -3813,8 +3791,8 @@
       <c r="Z6" s="13" t="n"/>
       <c r="AA6" s="13" t="n"/>
       <c r="AB6" s="14" t="n"/>
-      <c r="AC6" s="90" t="n"/>
-      <c r="AD6" s="91" t="n"/>
+      <c r="AC6" s="89" t="n"/>
+      <c r="AD6" s="90" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="83">
       <c r="A7" s="2" t="n"/>
@@ -3885,8 +3863,8 @@
       <c r="Z8" s="13" t="n"/>
       <c r="AA8" s="13" t="n"/>
       <c r="AB8" s="14" t="n"/>
-      <c r="AC8" s="90" t="n"/>
-      <c r="AD8" s="91" t="n"/>
+      <c r="AC8" s="89" t="n"/>
+      <c r="AD8" s="90" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="83">
       <c r="A9" s="2" t="n"/>
@@ -3917,8 +3895,8 @@
       <c r="Z9" s="13" t="n"/>
       <c r="AA9" s="13" t="n"/>
       <c r="AB9" s="14" t="n"/>
-      <c r="AC9" s="90" t="n"/>
-      <c r="AD9" s="91" t="n"/>
+      <c r="AC9" s="89" t="n"/>
+      <c r="AD9" s="90" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="83">
       <c r="A10" s="2" t="n"/>
@@ -3953,8 +3931,8 @@
       <c r="Z10" s="13" t="n"/>
       <c r="AA10" s="13" t="n"/>
       <c r="AB10" s="14" t="n"/>
-      <c r="AC10" s="90" t="n"/>
-      <c r="AD10" s="91" t="n"/>
+      <c r="AC10" s="89" t="n"/>
+      <c r="AD10" s="90" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="83">
       <c r="A11" s="2" t="n"/>
@@ -3993,8 +3971,8 @@
       <c r="Z11" s="13" t="n"/>
       <c r="AA11" s="13" t="n"/>
       <c r="AB11" s="14" t="n"/>
-      <c r="AC11" s="90" t="n"/>
-      <c r="AD11" s="91" t="n"/>
+      <c r="AC11" s="89" t="n"/>
+      <c r="AD11" s="90" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="83">
       <c r="A12" s="2" t="n"/>
@@ -4033,8 +4011,8 @@
       <c r="Z12" s="13" t="n"/>
       <c r="AA12" s="13" t="n"/>
       <c r="AB12" s="14" t="n"/>
-      <c r="AC12" s="90" t="n"/>
-      <c r="AD12" s="91" t="n"/>
+      <c r="AC12" s="89" t="n"/>
+      <c r="AD12" s="90" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="83">
       <c r="A13" s="2" t="n"/>
@@ -4073,8 +4051,8 @@
       <c r="Z13" s="13" t="n"/>
       <c r="AA13" s="13" t="n"/>
       <c r="AB13" s="14" t="n"/>
-      <c r="AC13" s="90" t="n"/>
-      <c r="AD13" s="91" t="n"/>
+      <c r="AC13" s="89" t="n"/>
+      <c r="AD13" s="90" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="83">
       <c r="A14" s="2" t="n"/>
@@ -4105,8 +4083,8 @@
       <c r="Z14" s="13" t="n"/>
       <c r="AA14" s="13" t="n"/>
       <c r="AB14" s="14" t="n"/>
-      <c r="AC14" s="90" t="n"/>
-      <c r="AD14" s="91" t="n"/>
+      <c r="AC14" s="89" t="n"/>
+      <c r="AD14" s="90" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="83">
       <c r="A15" s="2" t="n"/>
@@ -4137,8 +4115,8 @@
       <c r="Z15" s="13" t="n"/>
       <c r="AA15" s="13" t="n"/>
       <c r="AB15" s="14" t="n"/>
-      <c r="AC15" s="90" t="n"/>
-      <c r="AD15" s="91" t="n"/>
+      <c r="AC15" s="89" t="n"/>
+      <c r="AD15" s="90" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="83">
       <c r="A16" s="2" t="n"/>
@@ -4173,8 +4151,8 @@
       <c r="Z16" s="13" t="n"/>
       <c r="AA16" s="13" t="n"/>
       <c r="AB16" s="14" t="n"/>
-      <c r="AC16" s="90" t="n"/>
-      <c r="AD16" s="91" t="n"/>
+      <c r="AC16" s="89" t="n"/>
+      <c r="AD16" s="90" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="83">
       <c r="A17" s="2" t="n"/>
@@ -4213,8 +4191,8 @@
       <c r="Z17" s="13" t="n"/>
       <c r="AA17" s="13" t="n"/>
       <c r="AB17" s="14" t="n"/>
-      <c r="AC17" s="90" t="n"/>
-      <c r="AD17" s="91" t="n"/>
+      <c r="AC17" s="89" t="n"/>
+      <c r="AD17" s="90" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="83">
       <c r="A18" s="2" t="n"/>
@@ -4245,8 +4223,8 @@
       <c r="Z18" s="13" t="n"/>
       <c r="AA18" s="13" t="n"/>
       <c r="AB18" s="14" t="n"/>
-      <c r="AC18" s="90" t="n"/>
-      <c r="AD18" s="91" t="n"/>
+      <c r="AC18" s="89" t="n"/>
+      <c r="AD18" s="90" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="83">
       <c r="A19" s="2" t="n"/>
@@ -4277,8 +4255,8 @@
       <c r="Z19" s="13" t="n"/>
       <c r="AA19" s="13" t="n"/>
       <c r="AB19" s="14" t="n"/>
-      <c r="AC19" s="90" t="n"/>
-      <c r="AD19" s="91" t="n"/>
+      <c r="AC19" s="89" t="n"/>
+      <c r="AD19" s="90" t="n"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="83">
       <c r="A20" s="2" t="n"/>
@@ -4313,8 +4291,8 @@
       <c r="Z20" s="13" t="n"/>
       <c r="AA20" s="13" t="n"/>
       <c r="AB20" s="14" t="n"/>
-      <c r="AC20" s="90" t="n"/>
-      <c r="AD20" s="91" t="n"/>
+      <c r="AC20" s="89" t="n"/>
+      <c r="AD20" s="90" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="83">
       <c r="A21" s="2" t="n"/>
@@ -4353,8 +4331,8 @@
       <c r="Z21" s="13" t="n"/>
       <c r="AA21" s="13" t="n"/>
       <c r="AB21" s="14" t="n"/>
-      <c r="AC21" s="90" t="n"/>
-      <c r="AD21" s="91" t="n"/>
+      <c r="AC21" s="89" t="n"/>
+      <c r="AD21" s="90" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="83">
       <c r="A22" s="2" t="n"/>
@@ -4393,8 +4371,8 @@
       <c r="Z22" s="13" t="n"/>
       <c r="AA22" s="13" t="n"/>
       <c r="AB22" s="14" t="n"/>
-      <c r="AC22" s="90" t="n"/>
-      <c r="AD22" s="91" t="n"/>
+      <c r="AC22" s="89" t="n"/>
+      <c r="AD22" s="90" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="83">
       <c r="A23" s="2" t="n"/>
@@ -4433,8 +4411,8 @@
       <c r="Z23" s="13" t="n"/>
       <c r="AA23" s="13" t="n"/>
       <c r="AB23" s="14" t="n"/>
-      <c r="AC23" s="90" t="n"/>
-      <c r="AD23" s="91" t="n"/>
+      <c r="AC23" s="89" t="n"/>
+      <c r="AD23" s="90" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="83">
       <c r="A24" s="2" t="n"/>
@@ -4497,8 +4475,8 @@
       <c r="Z25" s="13" t="n"/>
       <c r="AA25" s="13" t="n"/>
       <c r="AB25" s="14" t="n"/>
-      <c r="AC25" s="90" t="n"/>
-      <c r="AD25" s="91" t="n"/>
+      <c r="AC25" s="89" t="n"/>
+      <c r="AD25" s="90" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="83">
       <c r="A26" s="2" t="n"/>
@@ -4573,8 +4551,8 @@
       <c r="Z27" s="13" t="n"/>
       <c r="AA27" s="13" t="n"/>
       <c r="AB27" s="14" t="n"/>
-      <c r="AC27" s="90" t="n"/>
-      <c r="AD27" s="91" t="n"/>
+      <c r="AC27" s="89" t="n"/>
+      <c r="AD27" s="90" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="83">
       <c r="A28" s="2" t="n"/>
@@ -4613,8 +4591,8 @@
       <c r="Z28" s="13" t="n"/>
       <c r="AA28" s="13" t="n"/>
       <c r="AB28" s="14" t="n"/>
-      <c r="AC28" s="90" t="n"/>
-      <c r="AD28" s="91" t="n"/>
+      <c r="AC28" s="89" t="n"/>
+      <c r="AD28" s="90" t="n"/>
     </row>
     <row r="29" ht="13.5" customHeight="1" s="83">
       <c r="A29" s="2" t="n"/>
@@ -4753,8 +4731,8 @@
       <c r="Z32" s="13" t="n"/>
       <c r="AA32" s="13" t="n"/>
       <c r="AB32" s="14" t="n"/>
-      <c r="AC32" s="90" t="n"/>
-      <c r="AD32" s="91" t="n"/>
+      <c r="AC32" s="89" t="n"/>
+      <c r="AD32" s="90" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="83">
       <c r="A33" s="2" t="n"/>
@@ -4793,8 +4771,8 @@
       <c r="Z33" s="13" t="n"/>
       <c r="AA33" s="13" t="n"/>
       <c r="AB33" s="14" t="n"/>
-      <c r="AC33" s="90" t="n"/>
-      <c r="AD33" s="91" t="n"/>
+      <c r="AC33" s="89" t="n"/>
+      <c r="AD33" s="90" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="83">
       <c r="A34" s="2" t="n"/>
@@ -5078,9 +5056,9 @@
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="13" t="n"/>
       <c r="E42" s="13" t="n"/>
-      <c r="F42" s="92" t="n"/>
-      <c r="G42" s="92" t="n"/>
-      <c r="H42" s="92" t="n"/>
+      <c r="F42" s="91" t="n"/>
+      <c r="G42" s="91" t="n"/>
+      <c r="H42" s="91" t="n"/>
       <c r="I42" s="13" t="n"/>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="13" t="n"/>
@@ -5506,38 +5484,38 @@
       <c r="B5" s="34" t="n"/>
       <c r="C5" s="14" t="n"/>
       <c r="D5" s="35" t="n"/>
-      <c r="E5" s="93" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　本施工計画書は学校法人 椙山女学園星が丘キャンパス 大学会館食堂</t>
         </is>
       </c>
-      <c r="F5" s="90" t="n"/>
-      <c r="G5" s="90" t="n"/>
-      <c r="H5" s="90" t="n"/>
-      <c r="I5" s="90" t="n"/>
-      <c r="J5" s="90" t="n"/>
-      <c r="K5" s="90" t="n"/>
-      <c r="L5" s="90" t="n"/>
-      <c r="M5" s="90" t="n"/>
-      <c r="N5" s="90" t="n"/>
-      <c r="O5" s="90" t="n"/>
-      <c r="P5" s="90" t="n"/>
-      <c r="Q5" s="90" t="n"/>
-      <c r="R5" s="90" t="n"/>
-      <c r="S5" s="90" t="n"/>
-      <c r="T5" s="90" t="n"/>
-      <c r="U5" s="90" t="n"/>
-      <c r="V5" s="90" t="n"/>
-      <c r="W5" s="90" t="n"/>
-      <c r="X5" s="90" t="n"/>
-      <c r="Y5" s="90" t="n"/>
-      <c r="Z5" s="90" t="n"/>
-      <c r="AA5" s="90" t="n"/>
-      <c r="AB5" s="90" t="n"/>
-      <c r="AC5" s="90" t="n"/>
-      <c r="AD5" s="90" t="n"/>
-      <c r="AE5" s="90" t="n"/>
-      <c r="AF5" s="91" t="n"/>
+      <c r="F5" s="89" t="n"/>
+      <c r="G5" s="89" t="n"/>
+      <c r="H5" s="89" t="n"/>
+      <c r="I5" s="89" t="n"/>
+      <c r="J5" s="89" t="n"/>
+      <c r="K5" s="89" t="n"/>
+      <c r="L5" s="89" t="n"/>
+      <c r="M5" s="89" t="n"/>
+      <c r="N5" s="89" t="n"/>
+      <c r="O5" s="89" t="n"/>
+      <c r="P5" s="89" t="n"/>
+      <c r="Q5" s="89" t="n"/>
+      <c r="R5" s="89" t="n"/>
+      <c r="S5" s="89" t="n"/>
+      <c r="T5" s="89" t="n"/>
+      <c r="U5" s="89" t="n"/>
+      <c r="V5" s="89" t="n"/>
+      <c r="W5" s="89" t="n"/>
+      <c r="X5" s="89" t="n"/>
+      <c r="Y5" s="89" t="n"/>
+      <c r="Z5" s="89" t="n"/>
+      <c r="AA5" s="89" t="n"/>
+      <c r="AB5" s="89" t="n"/>
+      <c r="AC5" s="89" t="n"/>
+      <c r="AD5" s="89" t="n"/>
+      <c r="AE5" s="89" t="n"/>
+      <c r="AF5" s="90" t="n"/>
       <c r="AG5" s="2" t="n"/>
       <c r="AH5" s="2" t="n"/>
       <c r="AI5" s="2" t="n"/>
@@ -6548,7 +6526,7 @@
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="14" t="n"/>
       <c r="D20" s="35" t="n"/>
-      <c r="E20" s="94" t="inlineStr">
+      <c r="E20" s="92" t="inlineStr">
         <is>
           <t>（ク）　日建設計　提出書類作成要領・受注者検査要領26</t>
         </is>
@@ -6969,7 +6947,7 @@
       <c r="C26" s="14" t="n"/>
       <c r="D26" s="47" t="n"/>
       <c r="E26" s="42" t="n"/>
-      <c r="F26" s="94" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>公共建築改修工事標準仕様書（建築工事編）（令和７年版）</t>
         </is>
@@ -7389,7 +7367,7 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
-      <c r="F32" s="94" t="inlineStr">
+      <c r="F32" s="92" t="inlineStr">
         <is>
           <t>公共建築工事標準仕様書（建築工事編）（令和７年版）</t>
         </is>
@@ -7486,8 +7464,8 @@
       <c r="Z33" s="2" t="n"/>
       <c r="AA33" s="2" t="n"/>
       <c r="AB33" s="2" t="n"/>
-      <c r="AC33" s="90" t="n"/>
-      <c r="AD33" s="91" t="n"/>
+      <c r="AC33" s="89" t="n"/>
+      <c r="AD33" s="90" t="n"/>
       <c r="AE33" s="2" t="n"/>
       <c r="AF33" s="2" t="n"/>
       <c r="AG33" s="2" t="n"/>
@@ -7528,7 +7506,7 @@
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
-      <c r="E34" s="94" t="inlineStr">
+      <c r="E34" s="92" t="inlineStr">
         <is>
           <t>（ス）　日本建築学会【要確認】</t>
         </is>
@@ -8757,9 +8735,9 @@
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="18" t="n"/>
       <c r="E52" s="18" t="n"/>
-      <c r="F52" s="95" t="n"/>
-      <c r="G52" s="95" t="n"/>
-      <c r="H52" s="95" t="n"/>
+      <c r="F52" s="93" t="n"/>
+      <c r="G52" s="93" t="n"/>
+      <c r="H52" s="93" t="n"/>
       <c r="I52" s="18" t="n"/>
       <c r="J52" s="18" t="n"/>
       <c r="K52" s="18" t="n"/>
@@ -9139,18 +9117,18 @@
           <t>工事名称</t>
         </is>
       </c>
-      <c r="D5" s="90" t="n"/>
-      <c r="E5" s="90" t="n"/>
-      <c r="F5" s="90" t="n"/>
-      <c r="G5" s="91" t="n"/>
+      <c r="D5" s="89" t="n"/>
+      <c r="E5" s="89" t="n"/>
+      <c r="F5" s="89" t="n"/>
+      <c r="G5" s="90" t="n"/>
       <c r="H5" s="12" t="inlineStr">
         <is>
           <t>：</t>
         </is>
       </c>
-      <c r="I5" s="96" t="inlineStr">
-        <is>
-          <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事【要確認】</t>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事</t>
         </is>
       </c>
       <c r="J5" s="18" t="n"/>
@@ -9180,10 +9158,10 @@
       <c r="A6" s="18" t="n"/>
       <c r="B6" s="18" t="n"/>
       <c r="C6" s="55" t="n"/>
-      <c r="D6" s="90" t="n"/>
-      <c r="E6" s="90" t="n"/>
-      <c r="F6" s="90" t="n"/>
-      <c r="G6" s="91" t="n"/>
+      <c r="D6" s="89" t="n"/>
+      <c r="E6" s="89" t="n"/>
+      <c r="F6" s="89" t="n"/>
+      <c r="G6" s="90" t="n"/>
       <c r="H6" s="18" t="n"/>
       <c r="I6" s="18" t="n"/>
       <c r="J6" s="18" t="n"/>
@@ -9217,10 +9195,10 @@
           <t>工事場所</t>
         </is>
       </c>
-      <c r="D7" s="90" t="n"/>
-      <c r="E7" s="90" t="n"/>
-      <c r="F7" s="90" t="n"/>
-      <c r="G7" s="91" t="n"/>
+      <c r="D7" s="89" t="n"/>
+      <c r="E7" s="89" t="n"/>
+      <c r="F7" s="89" t="n"/>
+      <c r="G7" s="90" t="n"/>
       <c r="H7" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -9258,10 +9236,10 @@
       <c r="A8" s="18" t="n"/>
       <c r="B8" s="18" t="n"/>
       <c r="C8" s="55" t="n"/>
-      <c r="D8" s="90" t="n"/>
-      <c r="E8" s="90" t="n"/>
-      <c r="F8" s="90" t="n"/>
-      <c r="G8" s="91" t="n"/>
+      <c r="D8" s="89" t="n"/>
+      <c r="E8" s="89" t="n"/>
+      <c r="F8" s="89" t="n"/>
+      <c r="G8" s="90" t="n"/>
       <c r="H8" s="18" t="n"/>
       <c r="I8" s="18" t="n"/>
       <c r="J8" s="18" t="n"/>
@@ -9295,10 +9273,10 @@
           <t>建築主</t>
         </is>
       </c>
-      <c r="D9" s="90" t="n"/>
-      <c r="E9" s="90" t="n"/>
-      <c r="F9" s="90" t="n"/>
-      <c r="G9" s="91" t="n"/>
+      <c r="D9" s="89" t="n"/>
+      <c r="E9" s="89" t="n"/>
+      <c r="F9" s="89" t="n"/>
+      <c r="G9" s="90" t="n"/>
       <c r="H9" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -9336,10 +9314,10 @@
       <c r="A10" s="18" t="n"/>
       <c r="B10" s="18" t="n"/>
       <c r="C10" s="55" t="n"/>
-      <c r="D10" s="90" t="n"/>
-      <c r="E10" s="90" t="n"/>
-      <c r="F10" s="90" t="n"/>
-      <c r="G10" s="91" t="n"/>
+      <c r="D10" s="89" t="n"/>
+      <c r="E10" s="89" t="n"/>
+      <c r="F10" s="89" t="n"/>
+      <c r="G10" s="90" t="n"/>
       <c r="H10" s="18" t="n"/>
       <c r="I10" s="18" t="n"/>
       <c r="J10" s="18" t="n"/>
@@ -9373,10 +9351,10 @@
           <t>設計</t>
         </is>
       </c>
-      <c r="D11" s="90" t="n"/>
-      <c r="E11" s="90" t="n"/>
-      <c r="F11" s="90" t="n"/>
-      <c r="G11" s="91" t="n"/>
+      <c r="D11" s="89" t="n"/>
+      <c r="E11" s="89" t="n"/>
+      <c r="F11" s="89" t="n"/>
+      <c r="G11" s="90" t="n"/>
       <c r="H11" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -9451,18 +9429,18 @@
           <t>監理</t>
         </is>
       </c>
-      <c r="D13" s="90" t="n"/>
-      <c r="E13" s="90" t="n"/>
-      <c r="F13" s="90" t="n"/>
-      <c r="G13" s="91" t="n"/>
-      <c r="H13" s="97" t="inlineStr">
+      <c r="D13" s="89" t="n"/>
+      <c r="E13" s="89" t="n"/>
+      <c r="F13" s="89" t="n"/>
+      <c r="G13" s="90" t="n"/>
+      <c r="H13" s="94" t="inlineStr">
         <is>
           <t>：</t>
         </is>
       </c>
-      <c r="I13" s="96" t="inlineStr">
-        <is>
-          <t>株式会社　日建設計【要確認】</t>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>株式会社　日建設計</t>
         </is>
       </c>
       <c r="J13" s="18" t="n"/>
@@ -9492,10 +9470,10 @@
       <c r="A14" s="18" t="n"/>
       <c r="B14" s="18" t="n"/>
       <c r="C14" s="55" t="n"/>
-      <c r="D14" s="90" t="n"/>
-      <c r="E14" s="90" t="n"/>
-      <c r="F14" s="90" t="n"/>
-      <c r="G14" s="91" t="n"/>
+      <c r="D14" s="89" t="n"/>
+      <c r="E14" s="89" t="n"/>
+      <c r="F14" s="89" t="n"/>
+      <c r="G14" s="90" t="n"/>
       <c r="H14" s="18" t="n"/>
       <c r="I14" s="18" t="n"/>
       <c r="J14" s="18" t="n"/>
@@ -9529,10 +9507,10 @@
           <t>施工</t>
         </is>
       </c>
-      <c r="D15" s="90" t="n"/>
-      <c r="E15" s="90" t="n"/>
-      <c r="F15" s="90" t="n"/>
-      <c r="G15" s="91" t="n"/>
+      <c r="D15" s="89" t="n"/>
+      <c r="E15" s="89" t="n"/>
+      <c r="F15" s="89" t="n"/>
+      <c r="G15" s="90" t="n"/>
       <c r="H15" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -9570,10 +9548,10 @@
       <c r="A16" s="18" t="n"/>
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="55" t="n"/>
-      <c r="D16" s="90" t="n"/>
-      <c r="E16" s="90" t="n"/>
-      <c r="F16" s="90" t="n"/>
-      <c r="G16" s="91" t="n"/>
+      <c r="D16" s="89" t="n"/>
+      <c r="E16" s="89" t="n"/>
+      <c r="F16" s="89" t="n"/>
+      <c r="G16" s="90" t="n"/>
       <c r="H16" s="18" t="n"/>
       <c r="I16" s="18" t="n"/>
       <c r="J16" s="18" t="n"/>
@@ -9607,10 +9585,10 @@
           <t>全体工期</t>
         </is>
       </c>
-      <c r="D17" s="90" t="n"/>
-      <c r="E17" s="90" t="n"/>
-      <c r="F17" s="90" t="n"/>
-      <c r="G17" s="91" t="n"/>
+      <c r="D17" s="89" t="n"/>
+      <c r="E17" s="89" t="n"/>
+      <c r="F17" s="89" t="n"/>
+      <c r="G17" s="90" t="n"/>
       <c r="H17" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -9621,7 +9599,7 @@
           <t>2026年11月9日</t>
         </is>
       </c>
-      <c r="J17" s="91" t="n"/>
+      <c r="J17" s="90" t="n"/>
       <c r="K17" s="12" t="inlineStr">
         <is>
           <t>から</t>
@@ -9633,12 +9611,12 @@
           <t>2027年3月26日</t>
         </is>
       </c>
-      <c r="N17" s="90" t="n"/>
-      <c r="O17" s="90" t="n"/>
-      <c r="P17" s="90" t="n"/>
-      <c r="Q17" s="90" t="n"/>
-      <c r="R17" s="90" t="n"/>
-      <c r="S17" s="91" t="n"/>
+      <c r="N17" s="89" t="n"/>
+      <c r="O17" s="89" t="n"/>
+      <c r="P17" s="89" t="n"/>
+      <c r="Q17" s="89" t="n"/>
+      <c r="R17" s="89" t="n"/>
+      <c r="S17" s="90" t="n"/>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n"/>
       <c r="V17" s="2" t="n"/>
@@ -9656,10 +9634,10 @@
       <c r="A18" s="18" t="n"/>
       <c r="B18" s="18" t="n"/>
       <c r="C18" s="55" t="n"/>
-      <c r="D18" s="90" t="n"/>
-      <c r="E18" s="90" t="n"/>
-      <c r="F18" s="90" t="n"/>
-      <c r="G18" s="91" t="n"/>
+      <c r="D18" s="89" t="n"/>
+      <c r="E18" s="89" t="n"/>
+      <c r="F18" s="89" t="n"/>
+      <c r="G18" s="90" t="n"/>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="n"/>
       <c r="J18" s="18" t="n"/>
@@ -9693,10 +9671,10 @@
           <t>建物用途</t>
         </is>
       </c>
-      <c r="D19" s="90" t="n"/>
-      <c r="E19" s="90" t="n"/>
-      <c r="F19" s="90" t="n"/>
-      <c r="G19" s="91" t="n"/>
+      <c r="D19" s="89" t="n"/>
+      <c r="E19" s="89" t="n"/>
+      <c r="F19" s="89" t="n"/>
+      <c r="G19" s="90" t="n"/>
       <c r="H19" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -9734,10 +9712,10 @@
       <c r="A20" s="18" t="n"/>
       <c r="B20" s="18" t="n"/>
       <c r="C20" s="55" t="n"/>
-      <c r="D20" s="90" t="n"/>
-      <c r="E20" s="90" t="n"/>
-      <c r="F20" s="90" t="n"/>
-      <c r="G20" s="91" t="n"/>
+      <c r="D20" s="89" t="n"/>
+      <c r="E20" s="89" t="n"/>
+      <c r="F20" s="89" t="n"/>
+      <c r="G20" s="90" t="n"/>
       <c r="H20" s="18" t="n"/>
       <c r="I20" s="18" t="n"/>
       <c r="J20" s="18" t="n"/>
@@ -9771,10 +9749,10 @@
           <t>構造</t>
         </is>
       </c>
-      <c r="D21" s="90" t="n"/>
-      <c r="E21" s="90" t="n"/>
-      <c r="F21" s="90" t="n"/>
-      <c r="G21" s="91" t="n"/>
+      <c r="D21" s="89" t="n"/>
+      <c r="E21" s="89" t="n"/>
+      <c r="F21" s="89" t="n"/>
+      <c r="G21" s="90" t="n"/>
       <c r="H21" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -9849,10 +9827,10 @@
           <t>規模</t>
         </is>
       </c>
-      <c r="D23" s="90" t="n"/>
-      <c r="E23" s="90" t="n"/>
-      <c r="F23" s="90" t="n"/>
-      <c r="G23" s="91" t="n"/>
+      <c r="D23" s="89" t="n"/>
+      <c r="E23" s="89" t="n"/>
+      <c r="F23" s="89" t="n"/>
+      <c r="G23" s="90" t="n"/>
       <c r="H23" s="38" t="inlineStr">
         <is>
           <t>：</t>
@@ -9932,9 +9910,9 @@
           <t>改修面積</t>
         </is>
       </c>
-      <c r="J24" s="98" t="inlineStr">
-        <is>
-          <t>910</t>
+      <c r="J24" s="47" t="inlineStr">
+        <is>
+          <t>675</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -9943,11 +9921,7 @@
         </is>
       </c>
       <c r="L24" s="23" t="n"/>
-      <c r="M24" s="99" t="inlineStr">
-        <is>
-          <t>（うち食堂 675㎡、外構 235㎡）【案】</t>
-        </is>
-      </c>
+      <c r="M24" s="23" t="n"/>
       <c r="N24" s="23" t="n"/>
       <c r="O24" s="18" t="n"/>
       <c r="P24" s="23" t="n"/>
@@ -10518,9 +10492,9 @@
       <c r="A40" s="2" t="n"/>
       <c r="B40" s="13" t="n"/>
       <c r="C40" s="13" t="n"/>
-      <c r="D40" s="92" t="n"/>
-      <c r="E40" s="92" t="n"/>
-      <c r="F40" s="92" t="n"/>
+      <c r="D40" s="91" t="n"/>
+      <c r="E40" s="91" t="n"/>
+      <c r="F40" s="91" t="n"/>
       <c r="G40" s="13" t="n"/>
       <c r="H40" s="13" t="n"/>
       <c r="I40" s="13" t="n"/>
@@ -10813,7 +10787,7 @@
       <c r="AB48" s="2" t="n"/>
       <c r="AC48" s="2" t="n"/>
       <c r="AD48" s="56" t="n"/>
-      <c r="AE48" s="91" t="n"/>
+      <c r="AE48" s="90" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="83">
       <c r="A49" s="2" t="n"/>
@@ -10846,7 +10820,7 @@
       <c r="AB49" s="2" t="n"/>
       <c r="AC49" s="2" t="n"/>
       <c r="AD49" s="56" t="n"/>
-      <c r="AE49" s="91" t="n"/>
+      <c r="AE49" s="90" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="83">
       <c r="A50" s="2" t="n"/>
@@ -10866,7 +10840,7 @@
           <t>会社名</t>
         </is>
       </c>
-      <c r="J50" s="100" t="n"/>
+      <c r="J50" s="95" t="n"/>
       <c r="K50" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -10895,7 +10869,7 @@
       <c r="AB50" s="2" t="n"/>
       <c r="AC50" s="2" t="n"/>
       <c r="AD50" s="56" t="n"/>
-      <c r="AE50" s="91" t="n"/>
+      <c r="AE50" s="90" t="n"/>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="83">
       <c r="A51" s="2" t="n"/>
@@ -10911,13 +10885,13 @@
           <t>現場名</t>
         </is>
       </c>
-      <c r="J51" s="100" t="n"/>
+      <c r="J51" s="95" t="n"/>
       <c r="K51" s="12" t="inlineStr">
         <is>
           <t>：</t>
         </is>
       </c>
-      <c r="L51" s="96" t="inlineStr">
+      <c r="L51" s="12" t="inlineStr">
         <is>
           <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事</t>
         </is>
@@ -10940,7 +10914,7 @@
       <c r="AB51" s="2" t="n"/>
       <c r="AC51" s="2" t="n"/>
       <c r="AD51" s="56" t="n"/>
-      <c r="AE51" s="91" t="n"/>
+      <c r="AE51" s="90" t="n"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="83">
       <c r="A52" s="2" t="n"/>
@@ -10956,7 +10930,7 @@
           <t>現場事務所</t>
         </is>
       </c>
-      <c r="J52" s="100" t="n"/>
+      <c r="J52" s="95" t="n"/>
       <c r="K52" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -10985,7 +10959,7 @@
       <c r="AB52" s="2" t="n"/>
       <c r="AC52" s="2" t="n"/>
       <c r="AD52" s="56" t="n"/>
-      <c r="AE52" s="91" t="n"/>
+      <c r="AE52" s="90" t="n"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="83">
       <c r="A53" s="2" t="n"/>
@@ -10999,9 +10973,9 @@
       <c r="I53" s="72" t="n"/>
       <c r="J53" s="56" t="n"/>
       <c r="K53" s="18" t="n"/>
-      <c r="L53" s="96" t="inlineStr">
-        <is>
-          <t>東邦ガス星が丘営業所【要確認】</t>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>東邦ガス星が丘営業所</t>
         </is>
       </c>
       <c r="M53" s="70" t="n"/>
@@ -11022,7 +10996,7 @@
       <c r="AB53" s="2" t="n"/>
       <c r="AC53" s="2" t="n"/>
       <c r="AD53" s="56" t="n"/>
-      <c r="AE53" s="91" t="n"/>
+      <c r="AE53" s="90" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="83">
       <c r="A54" s="2" t="n"/>
@@ -11038,7 +11012,7 @@
           <t>ＴＥＬ</t>
         </is>
       </c>
-      <c r="J54" s="100" t="n"/>
+      <c r="J54" s="95" t="n"/>
       <c r="K54" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11067,7 +11041,7 @@
       <c r="AB54" s="2" t="n"/>
       <c r="AC54" s="2" t="n"/>
       <c r="AD54" s="56" t="n"/>
-      <c r="AE54" s="91" t="n"/>
+      <c r="AE54" s="90" t="n"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="83">
       <c r="A55" s="2" t="n"/>
@@ -11083,7 +11057,7 @@
           <t>現場管理責任者</t>
         </is>
       </c>
-      <c r="J55" s="100" t="n"/>
+      <c r="J55" s="95" t="n"/>
       <c r="K55" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11112,7 +11086,7 @@
       <c r="AB55" s="2" t="n"/>
       <c r="AC55" s="2" t="n"/>
       <c r="AD55" s="56" t="n"/>
-      <c r="AE55" s="91" t="n"/>
+      <c r="AE55" s="90" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="83">
       <c r="A56" s="2" t="n"/>
@@ -11128,15 +11102,15 @@
           <t>監理技術者</t>
         </is>
       </c>
-      <c r="J56" s="100" t="n"/>
+      <c r="J56" s="95" t="n"/>
       <c r="K56" s="12" t="inlineStr">
         <is>
           <t>：</t>
         </is>
       </c>
-      <c r="L56" s="101" t="inlineStr">
-        <is>
-          <t>【要確認】</t>
+      <c r="L56" s="97" t="inlineStr">
+        <is>
+          <t>金子　冬平</t>
         </is>
       </c>
       <c r="M56" s="70" t="n"/>
@@ -11173,7 +11147,7 @@
           <t>主任</t>
         </is>
       </c>
-      <c r="J57" s="100" t="n"/>
+      <c r="J57" s="95" t="n"/>
       <c r="K57" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11218,7 +11192,7 @@
           <t>係員</t>
         </is>
       </c>
-      <c r="J58" s="100" t="n"/>
+      <c r="J58" s="95" t="n"/>
       <c r="K58" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11258,18 +11232,18 @@
       <c r="F59" s="18" t="n"/>
       <c r="G59" s="18" t="n"/>
       <c r="H59" s="18" t="n"/>
-      <c r="I59" s="97" t="inlineStr">
+      <c r="I59" s="94" t="inlineStr">
         <is>
           <t>担当工事長</t>
         </is>
       </c>
-      <c r="J59" s="91" t="n"/>
-      <c r="K59" s="97" t="inlineStr">
+      <c r="J59" s="90" t="n"/>
+      <c r="K59" s="94" t="inlineStr">
         <is>
           <t>：</t>
         </is>
       </c>
-      <c r="L59" s="97" t="inlineStr">
+      <c r="L59" s="94" t="inlineStr">
         <is>
           <t>新地　誠</t>
         </is>
@@ -11304,7 +11278,7 @@
       <c r="G60" s="18" t="n"/>
       <c r="H60" s="18" t="n"/>
       <c r="I60" s="18" t="n"/>
-      <c r="J60" s="91" t="n"/>
+      <c r="J60" s="90" t="n"/>
       <c r="K60" s="18" t="n"/>
       <c r="L60" s="18" t="n"/>
       <c r="M60" s="18" t="n"/>
@@ -11345,7 +11319,7 @@
           <t>会社名</t>
         </is>
       </c>
-      <c r="J61" s="100" t="n"/>
+      <c r="J61" s="95" t="n"/>
       <c r="K61" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11472,7 +11446,7 @@
           <t>代表取締役</t>
         </is>
       </c>
-      <c r="J64" s="100" t="n"/>
+      <c r="J64" s="95" t="n"/>
       <c r="K64" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11517,7 +11491,7 @@
           <t>主任技術者</t>
         </is>
       </c>
-      <c r="J65" s="100" t="n"/>
+      <c r="J65" s="95" t="n"/>
       <c r="K65" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11558,7 +11532,7 @@
           <t>安全衛生管理者</t>
         </is>
       </c>
-      <c r="J66" s="100" t="n"/>
+      <c r="J66" s="95" t="n"/>
       <c r="K66" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11599,7 +11573,7 @@
           <t>現場代理人</t>
         </is>
       </c>
-      <c r="J67" s="100" t="n"/>
+      <c r="J67" s="95" t="n"/>
       <c r="K67" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11640,7 +11614,7 @@
           <t>作業責任者(職長)</t>
         </is>
       </c>
-      <c r="J68" s="100" t="n"/>
+      <c r="J68" s="95" t="n"/>
       <c r="K68" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11681,7 +11655,7 @@
       <c r="G69" s="18" t="n"/>
       <c r="H69" s="18" t="n"/>
       <c r="I69" s="18" t="n"/>
-      <c r="J69" s="91" t="n"/>
+      <c r="J69" s="90" t="n"/>
       <c r="K69" s="18" t="n"/>
       <c r="L69" s="18" t="n"/>
       <c r="M69" s="18" t="n"/>
@@ -11714,7 +11688,7 @@
       <c r="G70" s="18" t="n"/>
       <c r="H70" s="18" t="n"/>
       <c r="I70" s="18" t="n"/>
-      <c r="J70" s="91" t="n"/>
+      <c r="J70" s="90" t="n"/>
       <c r="K70" s="18" t="n"/>
       <c r="L70" s="18" t="n"/>
       <c r="M70" s="18" t="n"/>
@@ -11755,7 +11729,7 @@
           <t>会社名</t>
         </is>
       </c>
-      <c r="J71" s="100" t="n"/>
+      <c r="J71" s="95" t="n"/>
       <c r="K71" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11882,7 +11856,7 @@
           <t>代表取締役</t>
         </is>
       </c>
-      <c r="J74" s="100" t="n"/>
+      <c r="J74" s="95" t="n"/>
       <c r="K74" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11927,7 +11901,7 @@
           <t>主任技術者</t>
         </is>
       </c>
-      <c r="J75" s="100" t="n"/>
+      <c r="J75" s="95" t="n"/>
       <c r="K75" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -11968,7 +11942,7 @@
           <t>安全衛生管理者</t>
         </is>
       </c>
-      <c r="J76" s="100" t="n"/>
+      <c r="J76" s="95" t="n"/>
       <c r="K76" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -12009,7 +11983,7 @@
           <t>現場代理人</t>
         </is>
       </c>
-      <c r="J77" s="100" t="n"/>
+      <c r="J77" s="95" t="n"/>
       <c r="K77" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -12050,7 +12024,7 @@
           <t>作業責任者(職長)</t>
         </is>
       </c>
-      <c r="J78" s="100" t="n"/>
+      <c r="J78" s="95" t="n"/>
       <c r="K78" s="12" t="inlineStr">
         <is>
           <t>：</t>
@@ -12091,7 +12065,7 @@
       <c r="G79" s="18" t="n"/>
       <c r="H79" s="18" t="n"/>
       <c r="I79" s="14" t="n"/>
-      <c r="J79" s="91" t="n"/>
+      <c r="J79" s="90" t="n"/>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="18" t="n"/>
       <c r="M79" s="18" t="n"/>
@@ -12124,7 +12098,7 @@
       <c r="G80" s="18" t="n"/>
       <c r="H80" s="18" t="n"/>
       <c r="I80" s="14" t="n"/>
-      <c r="J80" s="91" t="n"/>
+      <c r="J80" s="90" t="n"/>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="18" t="n"/>
       <c r="M80" s="18" t="n"/>
@@ -12157,7 +12131,7 @@
       <c r="G81" s="18" t="n"/>
       <c r="H81" s="18" t="n"/>
       <c r="I81" s="56" t="n"/>
-      <c r="J81" s="91" t="n"/>
+      <c r="J81" s="90" t="n"/>
       <c r="K81" s="18" t="n"/>
       <c r="L81" s="18" t="n"/>
       <c r="M81" s="18" t="n"/>
@@ -12190,8 +12164,8 @@
       <c r="G82" s="18" t="n"/>
       <c r="H82" s="18" t="n"/>
       <c r="I82" s="56" t="n"/>
-      <c r="J82" s="90" t="n"/>
-      <c r="K82" s="91" t="n"/>
+      <c r="J82" s="89" t="n"/>
+      <c r="K82" s="90" t="n"/>
       <c r="L82" s="18" t="n"/>
       <c r="M82" s="18" t="n"/>
       <c r="N82" s="18" t="n"/>
@@ -12223,8 +12197,8 @@
       <c r="G83" s="18" t="n"/>
       <c r="H83" s="18" t="n"/>
       <c r="I83" s="56" t="n"/>
-      <c r="J83" s="90" t="n"/>
-      <c r="K83" s="91" t="n"/>
+      <c r="J83" s="89" t="n"/>
+      <c r="K83" s="90" t="n"/>
       <c r="L83" s="18" t="n"/>
       <c r="M83" s="18" t="n"/>
       <c r="N83" s="18" t="n"/>
@@ -12256,7 +12230,7 @@
       <c r="G84" s="18" t="n"/>
       <c r="H84" s="18" t="n"/>
       <c r="I84" s="56" t="n"/>
-      <c r="J84" s="91" t="n"/>
+      <c r="J84" s="90" t="n"/>
       <c r="K84" s="18" t="n"/>
       <c r="L84" s="18" t="n"/>
       <c r="M84" s="18" t="n"/>
@@ -12289,7 +12263,7 @@
       <c r="G85" s="18" t="n"/>
       <c r="H85" s="18" t="n"/>
       <c r="I85" s="56" t="n"/>
-      <c r="J85" s="91" t="n"/>
+      <c r="J85" s="90" t="n"/>
       <c r="K85" s="18" t="n"/>
       <c r="L85" s="18" t="n"/>
       <c r="M85" s="18" t="n"/>
@@ -12322,7 +12296,7 @@
       <c r="G86" s="18" t="n"/>
       <c r="H86" s="18" t="n"/>
       <c r="I86" s="56" t="n"/>
-      <c r="J86" s="91" t="n"/>
+      <c r="J86" s="90" t="n"/>
       <c r="K86" s="18" t="n"/>
       <c r="L86" s="18" t="n"/>
       <c r="M86" s="18" t="n"/>
@@ -12355,7 +12329,7 @@
       <c r="G87" s="18" t="n"/>
       <c r="H87" s="18" t="n"/>
       <c r="I87" s="56" t="n"/>
-      <c r="J87" s="91" t="n"/>
+      <c r="J87" s="90" t="n"/>
       <c r="K87" s="18" t="n"/>
       <c r="L87" s="18" t="n"/>
       <c r="M87" s="18" t="n"/>
@@ -12388,7 +12362,7 @@
       <c r="G88" s="18" t="n"/>
       <c r="H88" s="18" t="n"/>
       <c r="I88" s="56" t="n"/>
-      <c r="J88" s="91" t="n"/>
+      <c r="J88" s="90" t="n"/>
       <c r="K88" s="18" t="n"/>
       <c r="L88" s="18" t="n"/>
       <c r="M88" s="18" t="n"/>
@@ -12421,7 +12395,7 @@
       <c r="G89" s="18" t="n"/>
       <c r="H89" s="18" t="n"/>
       <c r="I89" s="14" t="n"/>
-      <c r="J89" s="91" t="n"/>
+      <c r="J89" s="90" t="n"/>
       <c r="K89" s="14" t="n"/>
       <c r="L89" s="18" t="n"/>
       <c r="M89" s="18" t="n"/>
@@ -12454,7 +12428,7 @@
       <c r="G90" s="18" t="n"/>
       <c r="H90" s="18" t="n"/>
       <c r="I90" s="14" t="n"/>
-      <c r="J90" s="91" t="n"/>
+      <c r="J90" s="90" t="n"/>
       <c r="K90" s="14" t="n"/>
       <c r="L90" s="18" t="n"/>
       <c r="M90" s="18" t="n"/>
@@ -12487,7 +12461,7 @@
       <c r="G91" s="18" t="n"/>
       <c r="H91" s="18" t="n"/>
       <c r="I91" s="14" t="n"/>
-      <c r="J91" s="91" t="n"/>
+      <c r="J91" s="90" t="n"/>
       <c r="K91" s="14" t="n"/>
       <c r="L91" s="18" t="n"/>
       <c r="M91" s="18" t="n"/>
@@ -12761,7 +12735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="83" min="1" max="1"/>
@@ -12773,704 +12747,584 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="102" t="inlineStr">
+      <c r="A1" s="98" t="inlineStr">
         <is>
           <t>施工計画書 雛形の修正一覧（2026/10/31、計画書チェック担当）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="103" t="inlineStr">
+      <c r="A2" s="99" t="inlineStr">
         <is>
           <t>元：260904_施工計画書_雛形.xlsx。修正した所は各シートで赤字。「要確認」は決まっていないので、決まったら直して黒字に戻す</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="104" t="inlineStr">
+      <c r="A4" s="100" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B4" s="104" t="inlineStr">
+      <c r="B4" s="100" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="100" t="inlineStr">
         <is>
           <t>場所</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="D4" s="100" t="inlineStr">
         <is>
           <t>旧</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="100" t="inlineStr">
         <is>
           <t>新</t>
         </is>
       </c>
-      <c r="F4" s="104" t="inlineStr">
+      <c r="F4" s="100" t="inlineStr">
         <is>
           <t>根拠・案</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="n">
+      <c r="A5" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="105" t="inlineStr">
+      <c r="B5" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C5" s="105" t="inlineStr">
+      <c r="C5" s="101" t="inlineStr">
         <is>
           <t>第２章 H13（2-1 監理）</t>
         </is>
       </c>
-      <c r="D5" s="105" t="n"/>
-      <c r="E5" s="105" t="inlineStr">
+      <c r="D5" s="101" t="n"/>
+      <c r="E5" s="101" t="inlineStr">
         <is>
           <t>：</t>
         </is>
       </c>
-      <c r="F5" s="105" t="inlineStr">
+      <c r="F5" s="101" t="inlineStr">
         <is>
           <t>「：」が抜けていた</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="n">
+      <c r="A6" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="105" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>第２章 L55（2-3 現場管理責任者）</t>
         </is>
       </c>
-      <c r="D6" s="105" t="inlineStr">
+      <c r="D6" s="101" t="inlineStr">
         <is>
           <t>新池　誠【検査責任者】</t>
         </is>
       </c>
-      <c r="E6" s="105" t="inlineStr">
+      <c r="E6" s="101" t="inlineStr">
         <is>
           <t>金子　冬平（主任）【検査責任者】</t>
         </is>
       </c>
-      <c r="F6" s="105" t="inlineStr">
+      <c r="F6" s="101" t="inlineStr">
         <is>
           <t>小山さん回答 10/31：現場管理責任者・検査責任者とも金子。「新池 誠」は誤り</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="105" t="n">
+      <c r="A7" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="105" t="inlineStr">
+      <c r="B7" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C7" s="105" t="inlineStr">
+      <c r="C7" s="101" t="inlineStr">
         <is>
           <t>第２章 I59（2-3）</t>
         </is>
       </c>
-      <c r="D7" s="105" t="inlineStr">
+      <c r="D7" s="101" t="inlineStr">
         <is>
           <t>（空欄）</t>
         </is>
       </c>
-      <c r="E7" s="105" t="inlineStr">
+      <c r="E7" s="101" t="inlineStr">
         <is>
           <t>担当工事長</t>
         </is>
       </c>
-      <c r="F7" s="105" t="inlineStr">
+      <c r="F7" s="101" t="inlineStr">
         <is>
           <t>小山さん回答 10/31：新地 誠は担当工事長。現場説明書 4.(2)「工事長 新地 誠」</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="105" t="n">
+      <c r="A8" s="101" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="105" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C8" s="105" t="inlineStr">
+      <c r="C8" s="101" t="inlineStr">
         <is>
           <t>第２章 K59（2-3）</t>
         </is>
       </c>
-      <c r="D8" s="105" t="inlineStr">
+      <c r="D8" s="101" t="inlineStr">
         <is>
           <t>（空欄）</t>
         </is>
       </c>
-      <c r="E8" s="105" t="inlineStr">
+      <c r="E8" s="101" t="inlineStr">
         <is>
           <t>：</t>
         </is>
       </c>
-      <c r="F8" s="105" t="inlineStr">
+      <c r="F8" s="101" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="105" t="n">
+      <c r="A9" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="105" t="inlineStr">
+      <c r="B9" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C9" s="105" t="inlineStr">
+      <c r="C9" s="101" t="inlineStr">
         <is>
           <t>第２章 L59（2-3）</t>
         </is>
       </c>
-      <c r="D9" s="105" t="inlineStr">
+      <c r="D9" s="101" t="inlineStr">
         <is>
           <t>（空欄）</t>
         </is>
       </c>
-      <c r="E9" s="105" t="inlineStr">
+      <c r="E9" s="101" t="inlineStr">
         <is>
           <t>新地　誠</t>
         </is>
       </c>
-      <c r="F9" s="105" t="inlineStr">
+      <c r="F9" s="101" t="inlineStr">
         <is>
           <t>同上（雛形の「新池」は誤記）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="105" t="n">
+      <c r="A10" s="101" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="105" t="inlineStr">
+      <c r="B10" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C10" s="105" t="inlineStr">
+      <c r="C10" s="101" t="inlineStr">
         <is>
           <t>第１章 F26（1-2（コ））</t>
         </is>
       </c>
-      <c r="D10" s="105" t="inlineStr">
+      <c r="D10" s="101" t="inlineStr">
         <is>
           <t>公共建築改修工事標準仕様書（建築工事編）（令和４年版）</t>
         </is>
       </c>
-      <c r="E10" s="105" t="inlineStr">
+      <c r="E10" s="101" t="inlineStr">
         <is>
           <t>公共建築改修工事標準仕様書（建築工事編）（令和７年版）</t>
         </is>
       </c>
-      <c r="F10" s="105" t="inlineStr">
+      <c r="F10" s="101" t="inlineStr">
         <is>
           <t>設計図 意匠03 改修特記仕様書（特記仕様書の適用 b・1.1.1(4)）、見積要項書 2.(3)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="105" t="n">
+      <c r="A11" s="101" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="105" t="inlineStr">
+      <c r="B11" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C11" s="105" t="inlineStr">
+      <c r="C11" s="101" t="inlineStr">
         <is>
           <t>第１章 F32（1-2（シ））</t>
         </is>
       </c>
-      <c r="D11" s="105" t="inlineStr">
+      <c r="D11" s="101" t="inlineStr">
         <is>
           <t>公共建築工事標準仕様書（建築工事編）（令和４年版）</t>
         </is>
       </c>
-      <c r="E11" s="105" t="inlineStr">
+      <c r="E11" s="101" t="inlineStr">
         <is>
           <t>公共建築工事標準仕様書（建築工事編）（令和７年版）</t>
         </is>
       </c>
-      <c r="F11" s="105" t="inlineStr">
+      <c r="F11" s="101" t="inlineStr">
         <is>
           <t>設計図 意匠03 改修特記仕様書（特記仕様書の適用 b・1.1.1(4)）、見積要項書 2.(3)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="105" t="n">
+      <c r="A12" s="101" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="105" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C12" s="105" t="inlineStr">
+      <c r="C12" s="101" t="inlineStr">
         <is>
           <t>第１章 E20（1-2（ク））</t>
         </is>
       </c>
-      <c r="D12" s="105" t="inlineStr">
+      <c r="D12" s="101" t="inlineStr">
         <is>
           <t>（ク）　日建設計　提出書類作成要領・受注者検査要領</t>
         </is>
       </c>
-      <c r="E12" s="105" t="inlineStr">
+      <c r="E12" s="101" t="inlineStr">
         <is>
           <t>（ク）　日建設計　提出書類作成要領・受注者検査要領26</t>
         </is>
       </c>
-      <c r="F12" s="105" t="inlineStr">
+      <c r="F12" s="101" t="inlineStr">
         <is>
           <t>特記 1.1.1(4)(ク)・見積要項書 2.(3)「提出書類作成要領・受注者検査要領 26」。版を明記</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="105" t="n">
+      <c r="A13" s="101" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="105" t="inlineStr">
+      <c r="B13" s="101" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C13" s="105" t="inlineStr">
-        <is>
-          <t>第２章 J24（2-1 改修面積）【案】</t>
-        </is>
-      </c>
-      <c r="D13" s="105" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="E13" s="105" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="F13" s="105" t="inlineStr">
-        <is>
-          <t>小山さん回答 10/31：675㎡ は食堂だけ、外構も含めると 910㎡（契約は食堂＋外構3エリア）</t>
+      <c r="C13" s="101" t="inlineStr">
+        <is>
+          <t>第２章 L56（2-3 監理技術者）</t>
+        </is>
+      </c>
+      <c r="D13" s="101" t="inlineStr">
+        <is>
+          <t>（空欄）</t>
+        </is>
+      </c>
+      <c r="E13" s="101" t="inlineStr">
+        <is>
+          <t>金子　冬平</t>
+        </is>
+      </c>
+      <c r="F13" s="101" t="inlineStr">
+        <is>
+          <t>小山さん回答 10/31：監理技術者は金子</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="105" t="n">
+      <c r="A14" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="105" t="inlineStr">
-        <is>
-          <t>修正</t>
-        </is>
-      </c>
-      <c r="C14" s="105" t="inlineStr">
-        <is>
-          <t>第２章 M24（2-1 改修面積の内訳）【案】</t>
-        </is>
-      </c>
-      <c r="D14" s="105" t="inlineStr">
-        <is>
-          <t>（空欄）</t>
-        </is>
-      </c>
-      <c r="E14" s="105" t="inlineStr">
-        <is>
-          <t>（うち食堂 675㎡、外構 235㎡）【案】</t>
-        </is>
-      </c>
-      <c r="F14" s="105" t="inlineStr">
-        <is>
-          <t>内訳を併記して誤解を防ぐ案。食堂だけの計画書なら 675㎡ のままにする</t>
+      <c r="B14" s="101" t="inlineStr">
+        <is>
+          <t>変更なし</t>
+        </is>
+      </c>
+      <c r="C14" s="101" t="inlineStr">
+        <is>
+          <t>第２章 I17・M17（2-1 全体工期）</t>
+        </is>
+      </c>
+      <c r="D14" s="101" t="inlineStr">
+        <is>
+          <t>2026年11月9日 から 2027年3月26日</t>
+        </is>
+      </c>
+      <c r="E14" s="101" t="inlineStr">
+        <is>
+          <t>（変更なし）</t>
+        </is>
+      </c>
+      <c r="F14" s="101" t="inlineStr">
+        <is>
+          <t>小山さん確認 10/31：着工 2026/11/9・竣工 2027/3/26。雛形はもともと正しい</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="105" t="n">
+      <c r="A15" s="101" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="105" t="inlineStr">
-        <is>
-          <t>変更なし</t>
-        </is>
-      </c>
-      <c r="C15" s="105" t="inlineStr">
-        <is>
-          <t>第２章 I17・M17（2-1 全体工期）</t>
-        </is>
-      </c>
-      <c r="D15" s="105" t="inlineStr">
-        <is>
-          <t>2026年11月9日 から 2027年3月26日</t>
-        </is>
-      </c>
-      <c r="E15" s="105" t="inlineStr">
+      <c r="B15" s="101" t="inlineStr">
+        <is>
+          <t>確認のみ（変更なし）</t>
+        </is>
+      </c>
+      <c r="C15" s="101" t="inlineStr">
+        <is>
+          <t>第１章 E13</t>
+        </is>
+      </c>
+      <c r="D15" s="101" t="inlineStr">
+        <is>
+          <t>（イ）　民間（七会）連合協定工事請負契約約款（2025年（令和7年）12月改正）</t>
+        </is>
+      </c>
+      <c r="E15" s="101" t="inlineStr">
         <is>
           <t>（変更なし）</t>
         </is>
       </c>
-      <c r="F15" s="105" t="inlineStr">
-        <is>
-          <t>小山さん確認 10/31：着工 2026/11/9・竣工 2027/3/26。雛形はもともと正しい</t>
+      <c r="F15" s="101" t="inlineStr">
+        <is>
+          <t>七会約款 2025年（令和7年）12月改正：特記・見積要項書と一致</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="105" t="n">
+      <c r="A16" s="101" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="105" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
         <is>
           <t>確認のみ（変更なし）</t>
         </is>
       </c>
-      <c r="C16" s="105" t="inlineStr">
-        <is>
-          <t>第１章 E13</t>
-        </is>
-      </c>
-      <c r="D16" s="105" t="inlineStr">
-        <is>
-          <t>（イ）　民間（七会）連合協定工事請負契約約款（2025年（令和7年）12月改正）</t>
-        </is>
-      </c>
-      <c r="E16" s="105" t="inlineStr">
+      <c r="C16" s="101" t="inlineStr">
+        <is>
+          <t>第１章 F22</t>
+        </is>
+      </c>
+      <c r="D16" s="101" t="inlineStr">
+        <is>
+          <t>（公共建築協会編）（令和５年版）</t>
+        </is>
+      </c>
+      <c r="E16" s="101" t="inlineStr">
         <is>
           <t>（変更なし）</t>
         </is>
       </c>
-      <c r="F16" s="105" t="inlineStr">
-        <is>
-          <t>七会約款 2025年（令和7年）12月改正：特記・見積要項書と一致</t>
+      <c r="F16" s="101" t="inlineStr">
+        <is>
+          <t>共仕 令和5年版（1章のみ、1.3.12 不適用）：特記・見積要項書と一致</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="105" t="n">
+      <c r="A17" s="101" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="105" t="inlineStr">
+      <c r="B17" s="101" t="inlineStr">
         <is>
           <t>確認のみ（変更なし）</t>
         </is>
       </c>
-      <c r="C17" s="105" t="inlineStr">
-        <is>
-          <t>第１章 F22</t>
-        </is>
-      </c>
-      <c r="D17" s="105" t="inlineStr">
-        <is>
-          <t>（公共建築協会編）（令和５年版）</t>
-        </is>
-      </c>
-      <c r="E17" s="105" t="inlineStr">
+      <c r="C17" s="101" t="inlineStr">
+        <is>
+          <t>第１章 F29</t>
+        </is>
+      </c>
+      <c r="D17" s="101" t="inlineStr">
+        <is>
+          <t>建築物解体工事共通仕様書　（令和４年版）</t>
+        </is>
+      </c>
+      <c r="E17" s="101" t="inlineStr">
         <is>
           <t>（変更なし）</t>
         </is>
       </c>
-      <c r="F17" s="105" t="inlineStr">
-        <is>
-          <t>共仕 令和5年版（1章のみ、1.3.12 不適用）：特記・見積要項書と一致</t>
+      <c r="F17" s="101" t="inlineStr">
+        <is>
+          <t>解体共仕 令和4年版：特記・見積要項書と一致</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="105" t="n">
+      <c r="A18" s="101" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="105" t="inlineStr">
+      <c r="B18" s="101" t="inlineStr">
         <is>
           <t>確認のみ（変更なし）</t>
         </is>
       </c>
-      <c r="C18" s="105" t="inlineStr">
-        <is>
-          <t>第１章 F29</t>
-        </is>
-      </c>
-      <c r="D18" s="105" t="inlineStr">
-        <is>
-          <t>建築物解体工事共通仕様書　（令和４年版）</t>
-        </is>
-      </c>
-      <c r="E18" s="105" t="inlineStr">
+      <c r="C18" s="101" t="inlineStr">
+        <is>
+          <t>第２章 J24（2-1 改修面積）</t>
+        </is>
+      </c>
+      <c r="D18" s="101" t="inlineStr">
+        <is>
+          <t>675㎡</t>
+        </is>
+      </c>
+      <c r="E18" s="101" t="inlineStr">
         <is>
           <t>（変更なし）</t>
         </is>
       </c>
-      <c r="F18" s="105" t="inlineStr">
-        <is>
-          <t>解体共仕 令和4年版：特記・見積要項書と一致</t>
+      <c r="F18" s="101" t="inlineStr">
+        <is>
+          <t>小山さん回答 10/31：外構は入れない。675㎡ は食堂だけの面積</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="105" t="n">
+      <c r="A19" s="101" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="106" t="inlineStr">
+      <c r="B19" s="101" t="inlineStr">
+        <is>
+          <t>確認のみ（変更なし）</t>
+        </is>
+      </c>
+      <c r="C19" s="101" t="inlineStr">
+        <is>
+          <t>表紙 A5・第１章 E5・第２章 I5・L51（工事名）</t>
+        </is>
+      </c>
+      <c r="D19" s="101" t="inlineStr">
+        <is>
+          <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事</t>
+        </is>
+      </c>
+      <c r="E19" s="101" t="inlineStr">
+        <is>
+          <t>（変更なし）</t>
+        </is>
+      </c>
+      <c r="F19" s="101" t="inlineStr">
+        <is>
+          <t>小山さん回答 10/31：工事名は雛形のままでよい。外構は入れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="101" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="101" t="inlineStr">
+        <is>
+          <t>確認のみ（変更なし）</t>
+        </is>
+      </c>
+      <c r="C20" s="101" t="inlineStr">
+        <is>
+          <t>第２章 I13（2-1 監理）</t>
+        </is>
+      </c>
+      <c r="D20" s="101" t="inlineStr">
+        <is>
+          <t>株式会社　日建設計</t>
+        </is>
+      </c>
+      <c r="E20" s="101" t="inlineStr">
+        <is>
+          <t>（変更なし）</t>
+        </is>
+      </c>
+      <c r="F20" s="101" t="inlineStr">
+        <is>
+          <t>小山さん回答 10/31：監理は日建設計（「：」の追加だけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="101" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="101" t="inlineStr">
+        <is>
+          <t>確認のみ（変更なし）</t>
+        </is>
+      </c>
+      <c r="C21" s="101" t="inlineStr">
+        <is>
+          <t>第２章 L52～L53（2-3 現場事務所）</t>
+        </is>
+      </c>
+      <c r="D21" s="101" t="inlineStr">
+        <is>
+          <t>名古屋市千種区星が丘元町15-33 東邦ガス星が丘営業所</t>
+        </is>
+      </c>
+      <c r="E21" s="101" t="inlineStr">
+        <is>
+          <t>（変更なし）</t>
+        </is>
+      </c>
+      <c r="F21" s="101" t="inlineStr">
+        <is>
+          <t>小山さん回答 10/31：住所は合っている</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="101" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="102" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="C19" s="105" t="inlineStr">
+      <c r="C22" s="101" t="inlineStr">
         <is>
           <t>第１章 E34（1-2（ス）JASS）</t>
         </is>
       </c>
-      <c r="D19" s="105" t="inlineStr">
+      <c r="D22" s="101" t="inlineStr">
         <is>
           <t>（ス）　日本建築学会</t>
         </is>
       </c>
-      <c r="E19" s="105" t="inlineStr">
+      <c r="E22" s="101" t="inlineStr">
         <is>
           <t>（ス）　日本建築学会【要確認】</t>
         </is>
       </c>
-      <c r="F19" s="105" t="inlineStr">
+      <c r="F22" s="101" t="inlineStr">
         <is>
           <t>特記の適用図書は（ア）～（シ）の12項目で JASS は無い。案A：（ス）を削除し特記と同じ12項目にする（（ウ）はそのまま）。案B：工種別の基準として JASS を残すなら、（ウ）は特記どおり「（エ）から（シ）」のままとし、（ス）は契約図書でない「参考図書」と分かるように書く</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="105" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="106" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="C20" s="105" t="inlineStr">
-        <is>
-          <t>第２章 I5（2-1 工事名称）</t>
-        </is>
-      </c>
-      <c r="D20" s="105" t="inlineStr">
-        <is>
-          <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事</t>
-        </is>
-      </c>
-      <c r="E20" s="105" t="inlineStr">
-        <is>
-          <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事【要確認】</t>
-        </is>
-      </c>
-      <c r="F20" s="105" t="inlineStr">
-        <is>
-          <t>契約は1本で食堂＋外構3エリア。案：「椙山女学園/星が丘キャンパス大学会館食堂リニューアル工事、椙山女学園/星が丘キャンパス外構リニューアル工事」の2工事名を併記（見積要項書 1.(1)）。表紙 A5・第１章 E5・第２章 L51 も同じ書き方に合わせる</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="105" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="106" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="C21" s="105" t="inlineStr">
-        <is>
-          <t>第２章 I13（2-1 監理）</t>
-        </is>
-      </c>
-      <c r="D21" s="105" t="inlineStr">
-        <is>
-          <t>株式会社　日建設計</t>
-        </is>
-      </c>
-      <c r="E21" s="105" t="inlineStr">
-        <is>
-          <t>株式会社　日建設計【要確認】</t>
-        </is>
-      </c>
-      <c r="F21" s="105" t="inlineStr">
-        <is>
-          <t>見積要項書 10.(1)d)：工事約款の「監理者」は定めない。日建設計は「技術コンサルティング業務」の受託者。案：「技術コンサルティング：株式会社 日建設計」</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="105" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="106" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="C22" s="105" t="inlineStr">
-        <is>
-          <t>第２章 L52～L53（2-3 現場事務所）</t>
-        </is>
-      </c>
-      <c r="D22" s="105" t="inlineStr">
-        <is>
-          <t>東邦ガス星が丘営業所</t>
-        </is>
-      </c>
-      <c r="E22" s="105" t="inlineStr">
-        <is>
-          <t>東邦ガス星が丘営業所【要確認】</t>
-        </is>
-      </c>
-      <c r="F22" s="105" t="inlineStr">
-        <is>
-          <t>現場事務所の住所（名古屋市千種区星が丘元町15-33 東邦ガス星が丘営業所）が正しいか。工事場所は星が丘元町17番3号</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="105" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="106" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="C23" s="105" t="inlineStr">
-        <is>
-          <t>第２章 L56（2-3 監理技術者）</t>
-        </is>
-      </c>
-      <c r="D23" s="105" t="inlineStr">
-        <is>
-          <t>（空欄）</t>
-        </is>
-      </c>
-      <c r="E23" s="105" t="inlineStr">
-        <is>
-          <t>【要確認】</t>
-        </is>
-      </c>
-      <c r="F23" s="105" t="inlineStr">
-        <is>
-          <t>監理技術者の氏名が未記入</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="105" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="106" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="C24" s="105" t="inlineStr">
-        <is>
-          <t>表紙 A5（工事名）</t>
-        </is>
-      </c>
-      <c r="D24" s="105" t="inlineStr">
-        <is>
-          <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事</t>
-        </is>
-      </c>
-      <c r="E24" s="105" t="inlineStr">
-        <is>
-          <t>（文字は変えず赤字）</t>
-        </is>
-      </c>
-      <c r="F24" s="105" t="inlineStr">
-        <is>
-          <t>第２章 I5 と同じ。工事名の書き方が決まったら直す</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="105" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="106" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="C25" s="105" t="inlineStr">
-        <is>
-          <t>第１章 E5～E6（1-1 工事名）</t>
-        </is>
-      </c>
-      <c r="D25" s="105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　本施工計画書は学校法人 椙山女学園星が丘キャンパス 大学会館食堂</t>
-        </is>
-      </c>
-      <c r="E25" s="105" t="inlineStr">
-        <is>
-          <t>（文字は変えず赤字）</t>
-        </is>
-      </c>
-      <c r="F25" s="105" t="inlineStr">
-        <is>
-          <t>第２章 I5 と同じ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="105" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="106" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="C26" s="105" t="inlineStr">
-        <is>
-          <t>第２章 L51（2-3 現場名）</t>
-        </is>
-      </c>
-      <c r="D26" s="105" t="inlineStr">
-        <is>
-          <t>学校法人 椙山女学園星が丘キャンパス 大学会館食堂リニューアル工事</t>
-        </is>
-      </c>
-      <c r="E26" s="105" t="inlineStr">
-        <is>
-          <t>（文字は変えず赤字）</t>
-        </is>
-      </c>
-      <c r="F26" s="105" t="inlineStr">
-        <is>
-          <t>第２章 I5 と同じ</t>
         </is>
       </c>
     </row>
